--- a/Dropbox_content/Machines_Info.xlsx
+++ b/Dropbox_content/Machines_Info.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trainings\Self\ELK_Stack\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitContent\ELK\ELK\Dropbox_content\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -137,79 +137,79 @@
     <t>172.31.44.206</t>
   </si>
   <si>
-    <t>34.159.214.26</t>
-  </si>
-  <si>
-    <t>35.238.110.32</t>
-  </si>
-  <si>
     <t>35.208.241.252</t>
   </si>
   <si>
     <t>35.209.131.104</t>
   </si>
   <si>
-    <t>34.141.37.139</t>
-  </si>
-  <si>
-    <t>34.89.208.223</t>
-  </si>
-  <si>
-    <t>3.74.46.173</t>
-  </si>
-  <si>
-    <t>18.194.145.236</t>
-  </si>
-  <si>
-    <t>18.185.96.10</t>
-  </si>
-  <si>
-    <t>3.122.252.207</t>
-  </si>
-  <si>
-    <t>63.178.240.224</t>
-  </si>
-  <si>
-    <t>35.158.97.123</t>
-  </si>
-  <si>
-    <t>3.66.170.225</t>
-  </si>
-  <si>
     <t>m14</t>
   </si>
   <si>
     <t>172.31.32.73</t>
   </si>
   <si>
-    <t>35.159.117.55</t>
-  </si>
-  <si>
     <t>m15</t>
   </si>
   <si>
     <t>172.31.32.26</t>
   </si>
   <si>
-    <t>52.58.161.98</t>
-  </si>
-  <si>
     <t>m16</t>
   </si>
   <si>
     <t>172.31.33.253</t>
   </si>
   <si>
-    <t>3.123.153.244</t>
-  </si>
-  <si>
     <t>m17</t>
   </si>
   <si>
     <t>172.31.35.14</t>
   </si>
   <si>
-    <t>35.156.155.106</t>
+    <t>52.59.202.182</t>
+  </si>
+  <si>
+    <t>63.177.83.83</t>
+  </si>
+  <si>
+    <t>18.199.237.178</t>
+  </si>
+  <si>
+    <t>35.159.116.109</t>
+  </si>
+  <si>
+    <t>63.179.104.2</t>
+  </si>
+  <si>
+    <t>3.78.188.75</t>
+  </si>
+  <si>
+    <t>18.156.171.57</t>
+  </si>
+  <si>
+    <t>3.66.189.40</t>
+  </si>
+  <si>
+    <t>3.127.37.54</t>
+  </si>
+  <si>
+    <t>3.72.251.167</t>
+  </si>
+  <si>
+    <t>3.72.111.31</t>
+  </si>
+  <si>
+    <t>34.159.103.36</t>
+  </si>
+  <si>
+    <t>34.10.219.61</t>
+  </si>
+  <si>
+    <t>34.185.148.154</t>
+  </si>
+  <si>
+    <t>35.198.175.36</t>
   </si>
 </sst>
 </file>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -596,7 +596,7 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -613,7 +613,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -630,7 +630,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -647,7 +647,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -664,7 +664,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -681,7 +681,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -698,7 +698,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
@@ -715,7 +715,7 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
@@ -732,7 +732,7 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
@@ -749,7 +749,7 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
         <v>23</v>
@@ -766,7 +766,7 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
         <v>23</v>
@@ -783,7 +783,7 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
@@ -794,13 +794,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
         <v>23</v>
@@ -811,13 +811,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
         <v>23</v>
@@ -828,13 +828,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
@@ -845,13 +845,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
         <v>23</v>

--- a/Dropbox_content/Machines_Info.xlsx
+++ b/Dropbox_content/Machines_Info.xlsx
@@ -167,49 +167,49 @@
     <t>172.31.35.14</t>
   </si>
   <si>
-    <t>52.59.202.182</t>
-  </si>
-  <si>
-    <t>63.177.83.83</t>
-  </si>
-  <si>
-    <t>18.199.237.178</t>
-  </si>
-  <si>
-    <t>35.159.116.109</t>
-  </si>
-  <si>
-    <t>63.179.104.2</t>
-  </si>
-  <si>
-    <t>3.78.188.75</t>
-  </si>
-  <si>
-    <t>18.156.171.57</t>
-  </si>
-  <si>
-    <t>3.66.189.40</t>
-  </si>
-  <si>
-    <t>3.127.37.54</t>
-  </si>
-  <si>
-    <t>3.72.251.167</t>
-  </si>
-  <si>
-    <t>3.72.111.31</t>
-  </si>
-  <si>
-    <t>34.159.103.36</t>
-  </si>
-  <si>
-    <t>34.10.219.61</t>
-  </si>
-  <si>
-    <t>34.185.148.154</t>
-  </si>
-  <si>
-    <t>35.198.175.36</t>
+    <t>34.185.150.188</t>
+  </si>
+  <si>
+    <t>35.238.192.4</t>
+  </si>
+  <si>
+    <t>34.107.23.185</t>
+  </si>
+  <si>
+    <t>34.185.171.121</t>
+  </si>
+  <si>
+    <t>18.185.18.186</t>
+  </si>
+  <si>
+    <t>18.197.143.14</t>
+  </si>
+  <si>
+    <t>18.185.92.73</t>
+  </si>
+  <si>
+    <t>3.67.97.122</t>
+  </si>
+  <si>
+    <t>3.75.232.99</t>
+  </si>
+  <si>
+    <t>3.78.188.204</t>
+  </si>
+  <si>
+    <t>3.73.55.122</t>
+  </si>
+  <si>
+    <t>52.59.26.5</t>
+  </si>
+  <si>
+    <t>3.125.42.20</t>
+  </si>
+  <si>
+    <t>3.127.248.229</t>
+  </si>
+  <si>
+    <t>18.192.65.203</t>
   </si>
 </sst>
 </file>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -596,7 +596,7 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -613,7 +613,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -630,7 +630,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -647,7 +647,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -664,7 +664,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -681,7 +681,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -698,7 +698,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
@@ -715,7 +715,7 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
@@ -732,7 +732,7 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
@@ -749,7 +749,7 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
         <v>23</v>
@@ -766,7 +766,7 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
         <v>23</v>
@@ -783,7 +783,7 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
@@ -800,7 +800,7 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
         <v>23</v>
@@ -817,7 +817,7 @@
         <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
         <v>23</v>
@@ -834,7 +834,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
@@ -851,7 +851,7 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
         <v>23</v>

--- a/Dropbox_content/Machines_Info.xlsx
+++ b/Dropbox_content/Machines_Info.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitContent\ELK\ELK\Dropbox_content\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajay\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
   <si>
     <t>Machines Info</t>
   </si>
@@ -92,9 +92,6 @@
     <t>m7</t>
   </si>
   <si>
-    <t>172.31.42.47</t>
-  </si>
-  <si>
     <t>m1.ppk</t>
   </si>
   <si>
@@ -104,69 +101,12 @@
     <t>m8</t>
   </si>
   <si>
-    <t>m9</t>
-  </si>
-  <si>
-    <t>m10</t>
-  </si>
-  <si>
-    <t>m11</t>
-  </si>
-  <si>
-    <t>m12</t>
-  </si>
-  <si>
-    <t>m13</t>
-  </si>
-  <si>
-    <t>172.31.41.97</t>
-  </si>
-  <si>
-    <t>172.31.36.127</t>
-  </si>
-  <si>
-    <t>172.31.40.34</t>
-  </si>
-  <si>
-    <t>172.31.46.229</t>
-  </si>
-  <si>
-    <t>172.31.38.76</t>
-  </si>
-  <si>
-    <t>172.31.44.206</t>
-  </si>
-  <si>
     <t>35.208.241.252</t>
   </si>
   <si>
     <t>35.209.131.104</t>
   </si>
   <si>
-    <t>m14</t>
-  </si>
-  <si>
-    <t>172.31.32.73</t>
-  </si>
-  <si>
-    <t>m15</t>
-  </si>
-  <si>
-    <t>172.31.32.26</t>
-  </si>
-  <si>
-    <t>m16</t>
-  </si>
-  <si>
-    <t>172.31.33.253</t>
-  </si>
-  <si>
-    <t>m17</t>
-  </si>
-  <si>
-    <t>172.31.35.14</t>
-  </si>
-  <si>
     <t>34.185.150.188</t>
   </si>
   <si>
@@ -179,44 +119,77 @@
     <t>34.185.171.121</t>
   </si>
   <si>
-    <t>18.185.18.186</t>
-  </si>
-  <si>
-    <t>18.197.143.14</t>
-  </si>
-  <si>
-    <t>18.185.92.73</t>
-  </si>
-  <si>
-    <t>3.67.97.122</t>
-  </si>
-  <si>
-    <t>3.75.232.99</t>
-  </si>
-  <si>
-    <t>3.78.188.204</t>
-  </si>
-  <si>
-    <t>3.73.55.122</t>
-  </si>
-  <si>
-    <t>52.59.26.5</t>
-  </si>
-  <si>
-    <t>3.125.42.20</t>
-  </si>
-  <si>
-    <t>3.127.248.229</t>
-  </si>
-  <si>
-    <t>18.192.65.203</t>
+    <t>m1</t>
+  </si>
+  <si>
+    <t>m2</t>
+  </si>
+  <si>
+    <t>m3</t>
+  </si>
+  <si>
+    <t>m4</t>
+  </si>
+  <si>
+    <t>m5</t>
+  </si>
+  <si>
+    <t>m6</t>
+  </si>
+  <si>
+    <t>63.178.64.237</t>
+  </si>
+  <si>
+    <t>172.31.41.244</t>
+  </si>
+  <si>
+    <t>172.31.42.84</t>
+  </si>
+  <si>
+    <t>3.121.200.72</t>
+  </si>
+  <si>
+    <t>172.31.45.231</t>
+  </si>
+  <si>
+    <t>3.64.125.117</t>
+  </si>
+  <si>
+    <t>172.31.34.37</t>
+  </si>
+  <si>
+    <t>3.73.85.41</t>
+  </si>
+  <si>
+    <t>172.31.39.80</t>
+  </si>
+  <si>
+    <t>3.78.227.74</t>
+  </si>
+  <si>
+    <t>172.31.42.91</t>
+  </si>
+  <si>
+    <t>52.59.255.222</t>
+  </si>
+  <si>
+    <t>172.31.43.136</t>
+  </si>
+  <si>
+    <t>172.31.32.171</t>
+  </si>
+  <si>
+    <t>ubuntu@&lt;external-ip&gt;</t>
+  </si>
+  <si>
+    <t>hdu@&lt;external-ip&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,13 +205,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -250,14 +249,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -536,25 +541,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.08984375" customWidth="1"/>
     <col min="2" max="2" width="21.6328125" customWidth="1"/>
-    <col min="3" max="3" width="22.36328125" customWidth="1"/>
-    <col min="4" max="4" width="17.36328125" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" customWidth="1"/>
+    <col min="3" max="4" width="22.36328125" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
         <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -564,304 +572,302 @@
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s">
         <v>17</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="F16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1"/>
+    <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="D4" r:id="rId3"/>
+    <hyperlink ref="D5" r:id="rId4"/>
+    <hyperlink ref="D6" r:id="rId5"/>
+    <hyperlink ref="D7" r:id="rId6"/>
+    <hyperlink ref="D8" r:id="rId7"/>
+    <hyperlink ref="D10" r:id="rId8"/>
+    <hyperlink ref="D11" r:id="rId9"/>
+    <hyperlink ref="D12" r:id="rId10"/>
+    <hyperlink ref="D13" r:id="rId11"/>
+    <hyperlink ref="D14" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
--- a/Dropbox_content/Machines_Info.xlsx
+++ b/Dropbox_content/Machines_Info.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajay\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitContent\ELK\ELK\Dropbox_content\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="51">
   <si>
     <t>Machines Info</t>
   </si>
@@ -101,24 +101,6 @@
     <t>m8</t>
   </si>
   <si>
-    <t>35.208.241.252</t>
-  </si>
-  <si>
-    <t>35.209.131.104</t>
-  </si>
-  <si>
-    <t>34.185.150.188</t>
-  </si>
-  <si>
-    <t>35.238.192.4</t>
-  </si>
-  <si>
-    <t>34.107.23.185</t>
-  </si>
-  <si>
-    <t>34.185.171.121</t>
-  </si>
-  <si>
     <t>m1</t>
   </si>
   <si>
@@ -137,42 +119,24 @@
     <t>m6</t>
   </si>
   <si>
-    <t>63.178.64.237</t>
-  </si>
-  <si>
     <t>172.31.41.244</t>
   </si>
   <si>
     <t>172.31.42.84</t>
   </si>
   <si>
-    <t>3.121.200.72</t>
-  </si>
-  <si>
     <t>172.31.45.231</t>
   </si>
   <si>
-    <t>3.64.125.117</t>
-  </si>
-  <si>
     <t>172.31.34.37</t>
   </si>
   <si>
-    <t>3.73.85.41</t>
-  </si>
-  <si>
     <t>172.31.39.80</t>
   </si>
   <si>
-    <t>3.78.227.74</t>
-  </si>
-  <si>
     <t>172.31.42.91</t>
   </si>
   <si>
-    <t>52.59.255.222</t>
-  </si>
-  <si>
     <t>172.31.43.136</t>
   </si>
   <si>
@@ -183,6 +147,36 @@
   </si>
   <si>
     <t>hdu@&lt;external-ip&gt;</t>
+  </si>
+  <si>
+    <t>34.185.158.93</t>
+  </si>
+  <si>
+    <t>34.67.79.101</t>
+  </si>
+  <si>
+    <t>35.208.112.219</t>
+  </si>
+  <si>
+    <t>35.208.32.241</t>
+  </si>
+  <si>
+    <t>35.198.161.30</t>
+  </si>
+  <si>
+    <t>34.185.136.201</t>
+  </si>
+  <si>
+    <t>63.176.130.183</t>
+  </si>
+  <si>
+    <t>52.59.219.122</t>
+  </si>
+  <si>
+    <t>3.127.232.94</t>
+  </si>
+  <si>
+    <t>18.184.197.184</t>
   </si>
 </sst>
 </file>
@@ -588,10 +582,10 @@
         <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -608,10 +602,10 @@
         <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -628,10 +622,10 @@
         <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -648,10 +642,10 @@
         <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -668,10 +662,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -687,11 +681,11 @@
       <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>30</v>
+      <c r="C8" t="s">
+        <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -702,16 +696,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>37</v>
+      <c r="C9" t="s">
+        <v>47</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
@@ -722,16 +716,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
@@ -742,16 +736,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>42</v>
+      <c r="C11" t="s">
+        <v>49</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
@@ -762,16 +756,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>44</v>
+      <c r="C12" t="s">
+        <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
         <v>22</v>
@@ -782,16 +776,14 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="C13" s="5"/>
       <c r="D13" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
@@ -802,16 +794,14 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="C14" s="5"/>
       <c r="D14" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
         <v>22</v>
@@ -825,7 +815,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -841,7 +831,7 @@
         <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>

--- a/Dropbox_content/Machines_Info.xlsx
+++ b/Dropbox_content/Machines_Info.xlsx
@@ -535,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.08984375" customWidth="1"/>
@@ -545,7 +545,7 @@
     <col min="6" max="6" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D1" t="s">
         <v>19</v>
       </c>
@@ -556,7 +556,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,7 +574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -593,8 +593,11 @@
       <c r="F3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -613,8 +616,11 @@
       <c r="F4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -633,8 +639,11 @@
       <c r="F5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -653,8 +662,11 @@
       <c r="F6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -673,8 +685,11 @@
       <c r="F7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -693,8 +708,11 @@
       <c r="F8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -713,8 +731,11 @@
       <c r="F9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -733,8 +754,11 @@
       <c r="F10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -753,8 +777,11 @@
       <c r="F11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -773,8 +800,11 @@
       <c r="F12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -792,7 +822,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -810,7 +840,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -826,7 +856,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>

--- a/Dropbox_content/Machines_Info.xlsx
+++ b/Dropbox_content/Machines_Info.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitContent\ELK\ELK\Dropbox_content\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajay\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="52">
   <si>
     <t>Machines Info</t>
   </si>
@@ -149,34 +149,37 @@
     <t>hdu@&lt;external-ip&gt;</t>
   </si>
   <si>
-    <t>34.185.158.93</t>
-  </si>
-  <si>
-    <t>34.67.79.101</t>
+    <t>34.107.82.229</t>
+  </si>
+  <si>
+    <t>34.45.227.181</t>
+  </si>
+  <si>
+    <t>35.208.32.241</t>
   </si>
   <si>
     <t>35.208.112.219</t>
   </si>
   <si>
-    <t>35.208.32.241</t>
-  </si>
-  <si>
-    <t>35.198.161.30</t>
-  </si>
-  <si>
-    <t>34.185.136.201</t>
-  </si>
-  <si>
-    <t>63.176.130.183</t>
-  </si>
-  <si>
-    <t>52.59.219.122</t>
-  </si>
-  <si>
-    <t>3.127.232.94</t>
-  </si>
-  <si>
-    <t>18.184.197.184</t>
+    <t>35.234.106.241</t>
+  </si>
+  <si>
+    <t>34.185.221.156</t>
+  </si>
+  <si>
+    <t>18.194.143.81</t>
+  </si>
+  <si>
+    <t>54.93.48.236</t>
+  </si>
+  <si>
+    <t>35.159.19.23</t>
+  </si>
+  <si>
+    <t>18.196.103.32</t>
+  </si>
+  <si>
+    <t>52.59.3.196</t>
   </si>
 </sst>
 </file>
@@ -535,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.08984375" customWidth="1"/>
@@ -545,7 +548,7 @@
     <col min="6" max="6" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D1" t="s">
         <v>19</v>
       </c>
@@ -556,7 +559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,7 +577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -593,11 +596,8 @@
       <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="G3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -616,11 +616,8 @@
       <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -639,11 +636,8 @@
       <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -662,11 +656,8 @@
       <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -685,18 +676,15 @@
       <c r="F7" t="s">
         <v>18</v>
       </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -708,19 +696,16 @@
       <c r="F8" t="s">
         <v>18</v>
       </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" t="s">
-        <v>47</v>
+      <c r="C9" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>39</v>
@@ -731,19 +716,16 @@
       <c r="F9" t="s">
         <v>23</v>
       </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
-        <v>48</v>
+      <c r="C10" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>39</v>
@@ -754,19 +736,16 @@
       <c r="F10" t="s">
         <v>23</v>
       </c>
-      <c r="G10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
-        <v>49</v>
+      <c r="C11" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>39</v>
@@ -777,18 +756,15 @@
       <c r="F11" t="s">
         <v>23</v>
       </c>
-      <c r="G11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -800,18 +776,17 @@
       <c r="F12" t="s">
         <v>23</v>
       </c>
-      <c r="G12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="D13" s="3" t="s">
         <v>39</v>
       </c>
@@ -822,7 +797,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -840,7 +815,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -856,7 +831,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>

--- a/Dropbox_content/Machines_Info.xlsx
+++ b/Dropbox_content/Machines_Info.xlsx
@@ -149,44 +149,44 @@
     <t>hdu@&lt;external-ip&gt;</t>
   </si>
   <si>
-    <t>34.107.82.229</t>
-  </si>
-  <si>
-    <t>34.45.227.181</t>
-  </si>
-  <si>
     <t>35.208.32.241</t>
   </si>
   <si>
-    <t>35.208.112.219</t>
-  </si>
-  <si>
-    <t>35.234.106.241</t>
-  </si>
-  <si>
-    <t>34.185.221.156</t>
-  </si>
-  <si>
-    <t>18.194.143.81</t>
-  </si>
-  <si>
-    <t>54.93.48.236</t>
-  </si>
-  <si>
-    <t>35.159.19.23</t>
-  </si>
-  <si>
-    <t>18.196.103.32</t>
-  </si>
-  <si>
-    <t>52.59.3.196</t>
+    <t>34.159.39.68</t>
+  </si>
+  <si>
+    <t>34.16.73.77</t>
+  </si>
+  <si>
+    <t>35.206.89.7</t>
+  </si>
+  <si>
+    <t>34.141.76.121</t>
+  </si>
+  <si>
+    <t>34.89.215.123</t>
+  </si>
+  <si>
+    <t>63.177.91.252</t>
+  </si>
+  <si>
+    <t>3.73.120.62</t>
+  </si>
+  <si>
+    <t>3.74.157.215</t>
+  </si>
+  <si>
+    <t>63.178.121.144</t>
+  </si>
+  <si>
+    <t>3.120.27.65</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,6 +209,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -250,13 +256,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -585,7 +592,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>40</v>
@@ -605,7 +612,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>40</v>
@@ -625,7 +632,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>40</v>
@@ -645,7 +652,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>40</v>
@@ -704,8 +711,8 @@
       <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>48</v>
+      <c r="C9" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>39</v>
@@ -724,8 +731,8 @@
       <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>49</v>
+      <c r="C10" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>39</v>
@@ -744,8 +751,8 @@
       <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>47</v>
+      <c r="C11" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>39</v>
@@ -764,7 +771,7 @@
       <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -784,7 +791,7 @@
       <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
